--- a/supplementary_tables/Supplementary_Tables_S1_S18.xlsx
+++ b/supplementary_tables/Supplementary_Tables_S1_S18.xlsx
@@ -36,6 +36,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S16_metric_unit_guide" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S17_case_decision_boundary" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S18_environment_manifest" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table_S4e_naive_mlp" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6003,7 +6004,6 @@
       <c r="E90" t="n">
         <v>0.8551077953357222</v>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
         <v>0.871</v>
       </c>
@@ -6049,7 +6049,6 @@
       <c r="E91" t="n">
         <v>0.902439024390244</v>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
         <v>0.924</v>
       </c>
@@ -6095,7 +6094,6 @@
       <c r="E92" t="n">
         <v>0.6458264050548721</v>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
         <v>0.9419999999999999</v>
       </c>
@@ -6141,7 +6139,6 @@
       <c r="E93" t="n">
         <v>0.3520695007222605</v>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
         <v>0.256</v>
       </c>
@@ -6187,7 +6184,6 @@
       <c r="E94" t="n">
         <v>0.1788322549824511</v>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
         <v>0.536</v>
       </c>
@@ -6233,7 +6229,6 @@
       <c r="E95" t="n">
         <v>0.4382058069675574</v>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
         <v>0.63</v>
       </c>
@@ -6279,7 +6274,6 @@
       <c r="E96" t="n">
         <v>0.4517016156517738</v>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
         <v>0.474</v>
       </c>
@@ -6325,7 +6319,6 @@
       <c r="E97" t="n">
         <v>0.7700697697202045</v>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
         <v>0.859</v>
       </c>
@@ -6371,7 +6364,6 @@
       <c r="E98" t="n">
         <v>0.6985240233492779</v>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
         <v>0.736</v>
       </c>
@@ -6417,7 +6409,6 @@
       <c r="E99" t="n">
         <v>0.7008360219135269</v>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
         <v>0.79</v>
       </c>
@@ -6463,7 +6454,6 @@
       <c r="E100" t="n">
         <v>0.6734855334538878</v>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
         <v>0.667</v>
       </c>
@@ -6509,7 +6499,6 @@
       <c r="E101" t="n">
         <v>0.8623033394316458</v>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
         <v>0.916</v>
       </c>
@@ -6555,7 +6544,6 @@
       <c r="E102" t="n">
         <v>0.8578260869565217</v>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
         <v>0.956</v>
       </c>
@@ -6601,7 +6589,6 @@
       <c r="E103" t="n">
         <v>0.4196225087944947</v>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
         <v>0.576</v>
       </c>
@@ -6647,7 +6634,6 @@
       <c r="E104" t="n">
         <v>0.804860088365243</v>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
         <v>0.88</v>
       </c>
@@ -6693,7 +6679,6 @@
       <c r="E105" t="n">
         <v>0.9456790123456792</v>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
         <v>0.993</v>
       </c>
@@ -6739,7 +6724,6 @@
       <c r="E106" t="n">
         <v>0.6218126123432216</v>
       </c>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
         <v>0.552</v>
       </c>
@@ -6785,7 +6769,6 @@
       <c r="E107" t="n">
         <v>0.5572363431113107</v>
       </c>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
         <v>0.456</v>
       </c>
@@ -6831,7 +6814,6 @@
       <c r="E108" t="n">
         <v>0.9273527059450812</v>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
         <v>0.9379999999999999</v>
       </c>
@@ -6877,7 +6859,6 @@
       <c r="E109" t="n">
         <v>9.118758898412606</v>
       </c>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
         <v>7.44</v>
       </c>
@@ -6923,7 +6904,6 @@
       <c r="E110" t="n">
         <v>0.8359848801021843</v>
       </c>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
         <v>0.741</v>
       </c>
@@ -6969,7 +6949,6 @@
       <c r="E111" t="n">
         <v>0.4798305110695061</v>
       </c>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
         <v>0.713</v>
       </c>
@@ -9188,7 +9167,6 @@
       <c r="M2" t="n">
         <v>43.49841716654741</v>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>exact_v36_full_materialized_seed_mean_prediction</t>
@@ -9196,7 +9174,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>/mnt/afs/250010150/zhensheng/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/ppbr_az/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/ppbr_az/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -9364,9 +9342,6 @@
           <t>regression absolute-error visualization</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
       <c r="BM2" t="n">
         <v>17.17200683345259</v>
       </c>
@@ -9437,7 +9412,6 @@
       <c r="M3" t="n">
         <v>35.63617413480549</v>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>exact_v36_full_materialized_seed_mean_prediction</t>
@@ -9445,7 +9419,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>/mnt/afs/250010150/zhensheng/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/ppbr_az/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/ppbr_az/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -9613,9 +9587,6 @@
           <t>regression absolute-error visualization</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="n">
         <v>7.601550865194497</v>
       </c>
@@ -9686,7 +9657,6 @@
       <c r="M4" t="n">
         <v>3.28836214</v>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>exact_v36_full_materialized_seed_mean_prediction</t>
@@ -9694,7 +9664,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>/mnt/afs/250010150/zhensheng/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/clearance_hepatocyte_az/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/clearance_hepatocyte_az/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -9867,8 +9837,6 @@
           <t>Spearman endpoint: single-molecule absolute error is only a visualization aid, not endpoint-level evidence. Relabeled from module-sensitive to ranking-visualization to avoid a single-molecule Spearman overclaim.</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="n">
         <v>104.26629406</v>
       </c>
@@ -9939,7 +9907,6 @@
       <c r="M5" t="n">
         <v>95.58098898215944</v>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>exact_v36_full_materialized_seed_mean_prediction</t>
@@ -9947,7 +9914,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>/mnt/afs/250010150/zhensheng/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/clearance_microsome_az/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/clearance_microsome_az/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -10120,8 +10087,6 @@
           <t>Spearman endpoint: single-molecule absolute error is only a visualization aid, not endpoint-level evidence. All ablations have lower single-molecule absolute error than exact full; not module-sensitive.</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="n">
         <v>-6.203057782159433</v>
       </c>
@@ -10192,7 +10157,6 @@
       <c r="M6" t="n">
         <v>3.978488888888889</v>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>exact_v36_full_materialized_seed_mean_prediction</t>
@@ -10200,7 +10164,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>/mnt/afs/250010150/zhensheng/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/vdss_lombardo/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/vdss_lombardo/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -10373,8 +10337,6 @@
           <t>Spearman endpoint: single-molecule absolute error is only a visualization aid, not endpoint-level evidence. Relabeled from module-sensitive to ranking-visualization to avoid a single-molecule Spearman overclaim.</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="n">
         <v>46.04627811111111</v>
       </c>
@@ -10455,7 +10417,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>/mnt/afs/250010150/zhensheng/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/pgp_broccatelli/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/pgp_broccatelli/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -10714,7 +10676,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>/mnt/afs/250010150/zhensheng/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/hia_hou/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/hia_hou/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -10973,7 +10935,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>/mnt/afs/250010150/zhensheng/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/cyp3a4_substrate_carbonmangels/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/cyp3a4_substrate_carbonmangels/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -11222,7 +11184,6 @@
       <c r="M10" t="n">
         <v>0.04850213023681693</v>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>exact_v36_full_materialized_seed_mean_prediction</t>
@@ -11230,7 +11191,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>/mnt/afs/250010150/zhensheng/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/caco2_wang/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/caco2_wang/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -11398,9 +11359,6 @@
           <t>regression absolute-error visualization</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
       <c r="BM10" t="n">
         <v>0.8724349697631828</v>
       </c>
@@ -11471,7 +11429,6 @@
       <c r="M11" t="n">
         <v>66.20755471569653</v>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>exact_v36_full_materialized_seed_mean_prediction</t>
@@ -11479,7 +11436,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>/mnt/afs/250010150/zhensheng/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/clearance_microsome_az/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/clearance_microsome_az/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -11652,8 +11609,6 @@
           <t>Spearman endpoint: single-molecule absolute error is only a visualization aid, not endpoint-level evidence.</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="inlineStr"/>
       <c r="BM11" t="n">
         <v>95.49244528430346</v>
       </c>
@@ -15006,11 +14961,9 @@
       <c r="L2" t="n">
         <v>0.293194</v>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>0.894085</v>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>materialized full prediction for original molecule; perturbation uses reconstructed AMES task model</t>
@@ -20638,7 +20591,6 @@
           <t>original</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>TDC.Pgp</t>
@@ -20988,7 +20940,6 @@
           <t>original</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>TDC.Pgp</t>
@@ -22042,7 +21993,6 @@
           <t>original</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>TDC.Pgp</t>
@@ -22568,7 +22518,6 @@
           <t>original</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>TDC.Pgp</t>
@@ -23681,8 +23630,6 @@
           <t>repeated tabular ensemble; xgboost_500; 5 formal seeds with internal repeated scaffold fold-bag</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -23705,7 +23652,6 @@
       <c r="U2" t="b">
         <v>1</v>
       </c>
-      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23759,8 +23705,6 @@
           <t>ExtraTrees over chemical descriptors/fingerprints</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -23783,7 +23727,6 @@
       <c r="U3" t="b">
         <v>0</v>
       </c>
-      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23837,8 +23780,6 @@
           <t>Canonical backup uses chem fixed chemical endpoint: kpgt/chem_core_pair_torsion/extratrees/topk=all; formal seeds=101,202,303,404,505.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -23861,7 +23802,6 @@
       <c r="U4" t="b">
         <v>1</v>
       </c>
-      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23915,8 +23855,6 @@
           <t>Canonical backup uses chem fixed chemical endpoint: chemberta_kpgt/chem_core_pair_torsion/extratrees/topk=512; formal seeds=101,202,303,404,505.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -23939,7 +23877,6 @@
       <c r="U5" t="b">
         <v>1</v>
       </c>
-      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23993,8 +23930,6 @@
           <t>clearance family-transfer XGB; fingerprint-only; valid_adjusted selector</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -24017,7 +23952,6 @@
       <c r="U6" t="b">
         <v>0</v>
       </c>
-      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24071,8 +24005,6 @@
           <t>KPGT+EPT seedbag_5x5; equal seed-bag average</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -24095,7 +24027,6 @@
       <c r="U7" t="b">
         <v>1</v>
       </c>
-      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24149,8 +24080,6 @@
           <t>Canonical backup uses xl fixed chemical endpoint: xl_v4_kpgt/embed_chem_xl_full_chemical_prior/xgb/topk=1024; formal seeds=101,202,303,404,505.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -24173,7 +24102,6 @@
       <c r="U8" t="b">
         <v>1</v>
       </c>
-      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24227,8 +24155,6 @@
           <t>Canonical backup uses chem fixed chemical endpoint: kpgt_ept/chem_wide_chem/xgb/topk=all; formal seeds=101,202,303,404,505.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -24251,7 +24177,6 @@
       <c r="U9" t="b">
         <v>1</v>
       </c>
-      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24305,8 +24230,6 @@
           <t>zscore(0.8*AP_surrogate_seedbag + 0.1*XL + 0.1*descriptor_sidecar_v2)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -24329,7 +24252,6 @@
       <c r="U10" t="b">
         <v>1</v>
       </c>
-      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24383,8 +24305,6 @@
           <t>rank(0.4*K+E CE seedbag + 0.3*K+E FP/base_pred sidecar + 0.2*K+E AP + 0.1*tabular FP)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -24407,7 +24327,6 @@
       <c r="U11" t="b">
         <v>1</v>
       </c>
-      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24461,8 +24380,6 @@
           <t>CYP substrate family-transfer pooled XGB; fingerprint-only; task one-hot</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -24485,7 +24402,6 @@
       <c r="U12" t="b">
         <v>0</v>
       </c>
-      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24539,8 +24455,6 @@
           <t>logit(0.2*XL_K+E + 0.3*K+E CE seedbag + 0.3*K+E AP + 0.2*tabular FP)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -24563,7 +24477,6 @@
       <c r="U13" t="b">
         <v>1</v>
       </c>
-      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24617,8 +24530,6 @@
           <t>raw(0.6*XL_K+E + 0.2*K+E CE seedbag + 0.2*K+E descriptor sidecar)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -24641,7 +24552,6 @@
       <c r="U14" t="b">
         <v>1</v>
       </c>
-      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24695,8 +24605,6 @@
           <t>zscore(0.5*C+K metric_auto + 0.1*C+K Spearman seedbag + 0.4*C+K descriptor sidecar)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -24719,7 +24627,6 @@
       <c r="U15" t="b">
         <v>1</v>
       </c>
-      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24773,8 +24680,6 @@
           <t>Canonical backup uses xl fixed chemical endpoint: xl_v4_ept/embed_chem_xl_morgan_family/extratrees/topk=all; formal seeds=101,202,303,404,505.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -24797,7 +24702,6 @@
       <c r="U16" t="b">
         <v>1</v>
       </c>
-      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24851,8 +24755,6 @@
           <t>rank(0.1*selected_gated_5seed + 0.5*official_sidecar_bagged + 0.4*chem_logreg_trainonly); valid-only saturated-valid tie-break; true seed-varying 5-run final scores</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -24875,7 +24777,6 @@
       <c r="U17" t="b">
         <v>1</v>
       </c>
-      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24929,8 +24830,6 @@
           <t>Canonical backup uses xl fixed chemical endpoint: xl_v4_chemberta_kpgt/chem_xl_full_chemical_prior/xgb/topk=4096; formal seeds=101,202,303,404,505.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -24953,7 +24852,6 @@
       <c r="U18" t="b">
         <v>1</v>
       </c>
-      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25007,8 +24905,6 @@
           <t>raw(0.2*XL_K + 0.1*tabular FP + 0.3*K metric_auto + 0.4*K SmoothL1 seedbag)</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -25031,7 +24927,6 @@
       <c r="U19" t="b">
         <v>1</v>
       </c>
-      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25085,8 +24980,6 @@
           <t>logit(0.65*layerwise_selected_gated + 0.25*aux_K+E + 0.10*aux_K)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -25109,7 +25002,6 @@
       <c r="U20" t="b">
         <v>0</v>
       </c>
-      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -25163,8 +25055,6 @@
           <t>0.7*KPGT_seedbag + 0.3*fp_only</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -25187,7 +25077,6 @@
       <c r="U21" t="b">
         <v>1</v>
       </c>
-      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25241,8 +25130,6 @@
           <t>0.3*FP-XGB + 0.3*metric_auto(K+E) + 0.4*XL_v4</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -25265,7 +25152,6 @@
       <c r="U22" t="b">
         <v>0</v>
       </c>
-      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -25319,8 +25205,6 @@
           <t>rank(0.9*KPGT+EPT Spearman seedbag + 0.1*KPGT+EPT descriptor sidecar)</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -25343,7 +25227,6 @@
       <c r="U23" t="b">
         <v>1</v>
       </c>
-      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -25427,7 +25310,6 @@
       <c r="U24" t="b">
         <v>0</v>
       </c>
-      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -25511,7 +25393,6 @@
       <c r="U25" t="b">
         <v>0</v>
       </c>
-      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -25595,7 +25476,6 @@
       <c r="U26" t="b">
         <v>0</v>
       </c>
-      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -25679,7 +25559,6 @@
       <c r="U27" t="b">
         <v>0</v>
       </c>
-      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -25763,7 +25642,6 @@
       <c r="U28" t="b">
         <v>0</v>
       </c>
-      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -25847,7 +25725,6 @@
       <c r="U29" t="b">
         <v>0</v>
       </c>
-      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -25931,7 +25808,6 @@
       <c r="U30" t="b">
         <v>0</v>
       </c>
-      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -26015,7 +25891,6 @@
       <c r="U31" t="b">
         <v>0</v>
       </c>
-      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -26099,7 +25974,6 @@
       <c r="U32" t="b">
         <v>0</v>
       </c>
-      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -26183,7 +26057,6 @@
       <c r="U33" t="b">
         <v>0</v>
       </c>
-      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26267,7 +26140,6 @@
       <c r="U34" t="b">
         <v>0</v>
       </c>
-      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -26351,7 +26223,6 @@
       <c r="U35" t="b">
         <v>0</v>
       </c>
-      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26435,7 +26306,6 @@
       <c r="U36" t="b">
         <v>0</v>
       </c>
-      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -26519,7 +26389,6 @@
       <c r="U37" t="b">
         <v>0</v>
       </c>
-      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -26603,7 +26472,6 @@
       <c r="U38" t="b">
         <v>0</v>
       </c>
-      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -26687,7 +26555,6 @@
       <c r="U39" t="b">
         <v>0</v>
       </c>
-      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -26771,7 +26638,6 @@
       <c r="U40" t="b">
         <v>0</v>
       </c>
-      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -26855,7 +26721,6 @@
       <c r="U41" t="b">
         <v>0</v>
       </c>
-      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -26939,7 +26804,6 @@
       <c r="U42" t="b">
         <v>0</v>
       </c>
-      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -27023,7 +26887,6 @@
       <c r="U43" t="b">
         <v>0</v>
       </c>
-      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -27107,7 +26970,6 @@
       <c r="U44" t="b">
         <v>0</v>
       </c>
-      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -27191,7 +27053,6 @@
       <c r="U45" t="b">
         <v>0</v>
       </c>
-      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -27275,7 +27136,6 @@
       <c r="U46" t="b">
         <v>0</v>
       </c>
-      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -27359,7 +27219,6 @@
       <c r="U47" t="b">
         <v>0</v>
       </c>
-      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -27443,7 +27302,6 @@
       <c r="U48" t="b">
         <v>0</v>
       </c>
-      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -27527,7 +27385,6 @@
       <c r="U49" t="b">
         <v>0</v>
       </c>
-      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -27611,7 +27468,6 @@
       <c r="U50" t="b">
         <v>0</v>
       </c>
-      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -27695,7 +27551,6 @@
       <c r="U51" t="b">
         <v>0</v>
       </c>
-      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -27779,7 +27634,6 @@
       <c r="U52" t="b">
         <v>0</v>
       </c>
-      <c r="V52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -27863,7 +27717,6 @@
       <c r="U53" t="b">
         <v>0</v>
       </c>
-      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -27947,7 +27800,6 @@
       <c r="U54" t="b">
         <v>0</v>
       </c>
-      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -28031,7 +27883,6 @@
       <c r="U55" t="b">
         <v>0</v>
       </c>
-      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -28115,7 +27966,6 @@
       <c r="U56" t="b">
         <v>0</v>
       </c>
-      <c r="V56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -28199,7 +28049,6 @@
       <c r="U57" t="b">
         <v>0</v>
       </c>
-      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -28283,7 +28132,6 @@
       <c r="U58" t="b">
         <v>0</v>
       </c>
-      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -28367,7 +28215,6 @@
       <c r="U59" t="b">
         <v>0</v>
       </c>
-      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -28451,7 +28298,6 @@
       <c r="U60" t="b">
         <v>0</v>
       </c>
-      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -28535,7 +28381,6 @@
       <c r="U61" t="b">
         <v>0</v>
       </c>
-      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -28619,7 +28464,6 @@
       <c r="U62" t="b">
         <v>0</v>
       </c>
-      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -28703,7 +28547,6 @@
       <c r="U63" t="b">
         <v>0</v>
       </c>
-      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -28787,7 +28630,6 @@
       <c r="U64" t="b">
         <v>0</v>
       </c>
-      <c r="V64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -28871,7 +28713,6 @@
       <c r="U65" t="b">
         <v>0</v>
       </c>
-      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -28955,7 +28796,6 @@
       <c r="U66" t="b">
         <v>0</v>
       </c>
-      <c r="V66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -29039,7 +28879,6 @@
       <c r="U67" t="b">
         <v>0</v>
       </c>
-      <c r="V67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -29123,7 +28962,6 @@
       <c r="U68" t="b">
         <v>0</v>
       </c>
-      <c r="V68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -29207,7 +29045,6 @@
       <c r="U69" t="b">
         <v>0</v>
       </c>
-      <c r="V69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -29291,7 +29128,6 @@
       <c r="U70" t="b">
         <v>0</v>
       </c>
-      <c r="V70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -29375,7 +29211,6 @@
       <c r="U71" t="b">
         <v>0</v>
       </c>
-      <c r="V71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -29459,7 +29294,6 @@
       <c r="U72" t="b">
         <v>0</v>
       </c>
-      <c r="V72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -29543,7 +29377,6 @@
       <c r="U73" t="b">
         <v>0</v>
       </c>
-      <c r="V73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -29627,7 +29460,6 @@
       <c r="U74" t="b">
         <v>0</v>
       </c>
-      <c r="V74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -29711,7 +29543,6 @@
       <c r="U75" t="b">
         <v>0</v>
       </c>
-      <c r="V75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -29795,7 +29626,6 @@
       <c r="U76" t="b">
         <v>0</v>
       </c>
-      <c r="V76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -29879,7 +29709,6 @@
       <c r="U77" t="b">
         <v>0</v>
       </c>
-      <c r="V77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -29963,7 +29792,6 @@
       <c r="U78" t="b">
         <v>0</v>
       </c>
-      <c r="V78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -30047,7 +29875,6 @@
       <c r="U79" t="b">
         <v>0</v>
       </c>
-      <c r="V79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -30131,7 +29958,6 @@
       <c r="U80" t="b">
         <v>0</v>
       </c>
-      <c r="V80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -30215,7 +30041,6 @@
       <c r="U81" t="b">
         <v>0</v>
       </c>
-      <c r="V81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -30299,7 +30124,6 @@
       <c r="U82" t="b">
         <v>0</v>
       </c>
-      <c r="V82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -30383,7 +30207,6 @@
       <c r="U83" t="b">
         <v>0</v>
       </c>
-      <c r="V83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -30467,7 +30290,6 @@
       <c r="U84" t="b">
         <v>0</v>
       </c>
-      <c r="V84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -30551,7 +30373,6 @@
       <c r="U85" t="b">
         <v>0</v>
       </c>
-      <c r="V85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -30635,7 +30456,6 @@
       <c r="U86" t="b">
         <v>0</v>
       </c>
-      <c r="V86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -30719,7 +30539,6 @@
       <c r="U87" t="b">
         <v>0</v>
       </c>
-      <c r="V87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -30803,7 +30622,6 @@
       <c r="U88" t="b">
         <v>0</v>
       </c>
-      <c r="V88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -30887,7 +30705,6 @@
       <c r="U89" t="b">
         <v>0</v>
       </c>
-      <c r="V89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -30916,7 +30733,6 @@
       <c r="F90" t="n">
         <v>0.8551077953357222</v>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>0.871</v>
       </c>
@@ -30969,7 +30785,6 @@
       <c r="U90" t="b">
         <v>0</v>
       </c>
-      <c r="V90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -30998,7 +30813,6 @@
       <c r="F91" t="n">
         <v>0.902439024390244</v>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>0.924</v>
       </c>
@@ -31051,7 +30865,6 @@
       <c r="U91" t="b">
         <v>0</v>
       </c>
-      <c r="V91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -31080,7 +30893,6 @@
       <c r="F92" t="n">
         <v>0.6458264050548721</v>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>0.9419999999999999</v>
       </c>
@@ -31133,7 +30945,6 @@
       <c r="U92" t="b">
         <v>0</v>
       </c>
-      <c r="V92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -31162,7 +30973,6 @@
       <c r="F93" t="n">
         <v>0.3520695007222605</v>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>0.256</v>
       </c>
@@ -31215,7 +31025,6 @@
       <c r="U93" t="b">
         <v>0</v>
       </c>
-      <c r="V93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -31244,7 +31053,6 @@
       <c r="F94" t="n">
         <v>0.1788322549824511</v>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>0.536</v>
       </c>
@@ -31297,7 +31105,6 @@
       <c r="U94" t="b">
         <v>0</v>
       </c>
-      <c r="V94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -31326,7 +31133,6 @@
       <c r="F95" t="n">
         <v>0.4382058069675574</v>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>0.63</v>
       </c>
@@ -31379,7 +31185,6 @@
       <c r="U95" t="b">
         <v>0</v>
       </c>
-      <c r="V95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -31408,7 +31213,6 @@
       <c r="F96" t="n">
         <v>0.4517016156517738</v>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>0.474</v>
       </c>
@@ -31461,7 +31265,6 @@
       <c r="U96" t="b">
         <v>0</v>
       </c>
-      <c r="V96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -31490,7 +31293,6 @@
       <c r="F97" t="n">
         <v>0.7700697697202045</v>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>0.859</v>
       </c>
@@ -31543,7 +31345,6 @@
       <c r="U97" t="b">
         <v>0</v>
       </c>
-      <c r="V97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -31572,7 +31373,6 @@
       <c r="F98" t="n">
         <v>0.6985240233492779</v>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>0.736</v>
       </c>
@@ -31625,7 +31425,6 @@
       <c r="U98" t="b">
         <v>0</v>
       </c>
-      <c r="V98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -31654,7 +31453,6 @@
       <c r="F99" t="n">
         <v>0.7008360219135269</v>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>0.79</v>
       </c>
@@ -31707,7 +31505,6 @@
       <c r="U99" t="b">
         <v>0</v>
       </c>
-      <c r="V99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -31736,7 +31533,6 @@
       <c r="F100" t="n">
         <v>0.6734855334538878</v>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>0.667</v>
       </c>
@@ -31789,7 +31585,6 @@
       <c r="U100" t="b">
         <v>0</v>
       </c>
-      <c r="V100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -31818,7 +31613,6 @@
       <c r="F101" t="n">
         <v>0.8623033394316458</v>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>0.916</v>
       </c>
@@ -31871,7 +31665,6 @@
       <c r="U101" t="b">
         <v>0</v>
       </c>
-      <c r="V101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -31900,7 +31693,6 @@
       <c r="F102" t="n">
         <v>0.8578260869565217</v>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>0.956</v>
       </c>
@@ -31953,7 +31745,6 @@
       <c r="U102" t="b">
         <v>0</v>
       </c>
-      <c r="V102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -31982,7 +31773,6 @@
       <c r="F103" t="n">
         <v>0.4196225087944947</v>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>0.576</v>
       </c>
@@ -32035,7 +31825,6 @@
       <c r="U103" t="b">
         <v>0</v>
       </c>
-      <c r="V103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -32064,7 +31853,6 @@
       <c r="F104" t="n">
         <v>0.804860088365243</v>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>0.88</v>
       </c>
@@ -32117,7 +31905,6 @@
       <c r="U104" t="b">
         <v>0</v>
       </c>
-      <c r="V104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -32146,7 +31933,6 @@
       <c r="F105" t="n">
         <v>0.9456790123456792</v>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>0.993</v>
       </c>
@@ -32199,7 +31985,6 @@
       <c r="U105" t="b">
         <v>0</v>
       </c>
-      <c r="V105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -32228,7 +32013,6 @@
       <c r="F106" t="n">
         <v>0.6218126123432216</v>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>0.552</v>
       </c>
@@ -32281,7 +32065,6 @@
       <c r="U106" t="b">
         <v>0</v>
       </c>
-      <c r="V106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -32310,7 +32093,6 @@
       <c r="F107" t="n">
         <v>0.5572363431113107</v>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>0.456</v>
       </c>
@@ -32363,7 +32145,6 @@
       <c r="U107" t="b">
         <v>0</v>
       </c>
-      <c r="V107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -32392,7 +32173,6 @@
       <c r="F108" t="n">
         <v>0.9273527059450812</v>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>0.9379999999999999</v>
       </c>
@@ -32445,7 +32225,6 @@
       <c r="U108" t="b">
         <v>0</v>
       </c>
-      <c r="V108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -32474,7 +32253,6 @@
       <c r="F109" t="n">
         <v>9.118758898412606</v>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>7.44</v>
       </c>
@@ -32527,7 +32305,6 @@
       <c r="U109" t="b">
         <v>0</v>
       </c>
-      <c r="V109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -32556,7 +32333,6 @@
       <c r="F110" t="n">
         <v>0.8359848801021843</v>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>0.741</v>
       </c>
@@ -32609,7 +32385,6 @@
       <c r="U110" t="b">
         <v>0</v>
       </c>
-      <c r="V110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -32638,7 +32413,6 @@
       <c r="F111" t="n">
         <v>0.4798305110695061</v>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>0.713</v>
       </c>
@@ -32691,7 +32465,6 @@
       <c r="U111" t="b">
         <v>0</v>
       </c>
-      <c r="V111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -32775,7 +32548,6 @@
       <c r="U112" t="b">
         <v>0</v>
       </c>
-      <c r="V112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -32859,7 +32631,6 @@
       <c r="U113" t="b">
         <v>0</v>
       </c>
-      <c r="V113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -32943,7 +32714,6 @@
       <c r="U114" t="b">
         <v>0</v>
       </c>
-      <c r="V114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -33027,7 +32797,6 @@
       <c r="U115" t="b">
         <v>0</v>
       </c>
-      <c r="V115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -33111,7 +32880,6 @@
       <c r="U116" t="b">
         <v>0</v>
       </c>
-      <c r="V116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -33195,7 +32963,6 @@
       <c r="U117" t="b">
         <v>0</v>
       </c>
-      <c r="V117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -33279,7 +33046,6 @@
       <c r="U118" t="b">
         <v>0</v>
       </c>
-      <c r="V118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -33363,7 +33129,6 @@
       <c r="U119" t="b">
         <v>0</v>
       </c>
-      <c r="V119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -33447,7 +33212,6 @@
       <c r="U120" t="b">
         <v>0</v>
       </c>
-      <c r="V120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -33531,7 +33295,6 @@
       <c r="U121" t="b">
         <v>0</v>
       </c>
-      <c r="V121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -33615,7 +33378,6 @@
       <c r="U122" t="b">
         <v>0</v>
       </c>
-      <c r="V122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -33699,7 +33461,6 @@
       <c r="U123" t="b">
         <v>0</v>
       </c>
-      <c r="V123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -33783,7 +33544,6 @@
       <c r="U124" t="b">
         <v>0</v>
       </c>
-      <c r="V124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -33867,7 +33627,6 @@
       <c r="U125" t="b">
         <v>0</v>
       </c>
-      <c r="V125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -33951,7 +33710,6 @@
       <c r="U126" t="b">
         <v>0</v>
       </c>
-      <c r="V126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -34035,7 +33793,6 @@
       <c r="U127" t="b">
         <v>0</v>
       </c>
-      <c r="V127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -34119,7 +33876,6 @@
       <c r="U128" t="b">
         <v>0</v>
       </c>
-      <c r="V128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -34203,7 +33959,6 @@
       <c r="U129" t="b">
         <v>0</v>
       </c>
-      <c r="V129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -34287,7 +34042,6 @@
       <c r="U130" t="b">
         <v>0</v>
       </c>
-      <c r="V130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -34371,7 +34125,6 @@
       <c r="U131" t="b">
         <v>0</v>
       </c>
-      <c r="V131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -34455,7 +34208,6 @@
       <c r="U132" t="b">
         <v>0</v>
       </c>
-      <c r="V132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -34539,7 +34291,6 @@
       <c r="U133" t="b">
         <v>0</v>
       </c>
-      <c r="V133" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -35634,7 +35385,6 @@
           <t>blocked_numeric_mismatch</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>AqSol reconstruction previously numeric mismatch; not strict.</t>
@@ -35652,7 +35402,6 @@
           <t>blocked_rank_transform_external_scale</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>Rank-transformed endpoint; arbitrary-SMILES exact score not naturally defined on same rank scale.</t>
@@ -35670,7 +35419,6 @@
           <t>no_pdf_external_label</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>PDF text has no explicit AMES/mutagenicity labels for candidate molecules; not useful for external case.</t>
@@ -35688,7 +35436,6 @@
           <t>exact_reconstruction_pass</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>Exact pass and one strict case exists, but user asked to stop CYP3A4 expansion.</t>
@@ -41945,9 +41692,6 @@
           <t>Some matched replacements changed BBB scores</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>reconstruction_mismatch</t>
@@ -41980,9 +41724,6 @@
           <t>MiniMol boundary/wrong and Trimole exact replay correct in external comparison</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>exact external replay for original prediction; perturbation not compelling</t>
@@ -42015,9 +41756,6 @@
           <t>Boundary example with some Trimole-vs-MiniMol separation</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>P-gp exact replay available</t>
@@ -42050,9 +41788,6 @@
           <t>Potential regression cases from external drug labels</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>unavailable_or_proxy_required</t>
@@ -42085,9 +41820,6 @@
           <t>Revumenib and other high-binding candidates showed potential</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>near_reconstruction_or_proxy</t>
@@ -42183,7 +41915,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/mnt/afs/250010150/envs/trimole_bench310/bin/python</t>
+          <t>https://github.com/dchen0212/trimole_hybird</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -42245,7 +41977,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>/mnt/afs/250010150/envs/kpgt/bin/python</t>
+          <t>https://github.com/dchen0212/trimole_hybird</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -43284,6 +43016,3250 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>variant</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>n_runs</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>score_mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score_std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>top1_ref</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>direction_normalized_margin</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>diagnostic_margin_ge_0</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>delta_margin_vs_full</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>selection_protocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ames</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.871945</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.000583</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0009449999999999</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bbb_martins</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.927779</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.000477</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0037789999999999</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bioavailability_ma</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.722248</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.004048</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.2197519999999999</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>caco2_wang</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.283647</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.0276469999999999</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>clearance_hepatocyte_az</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.55204</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.009650000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0160399999999999</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>clearance_microsome_az</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.642814</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005773</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0128139999999999</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cyp2c9_substrate_carbonmangels</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.44337</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.023358</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.0306299999999999</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cyp2c9_veith</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.790586</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002608</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.06841399999999991</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cyp2d6_substrate_carbonmangels</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.7475309999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.00961</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0115309999999999</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cyp2d6_veith</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.719172</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005514</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.070828</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cyp3a4_substrate_carbonmangels</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.725249</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.00476</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0582489999999999</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cyp3a4_veith</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.884121</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.003206</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.0318789999999999</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dili</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.908609</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.00552</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.0473909999999999</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>half_life_obach</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.49139</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.009785</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.08460999999999989</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>herg</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.863358</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.002334</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.016642</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>hia_hou</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9942800000000001</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.001736</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.00128</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ld50_zhu</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.603071</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.003837</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.0510709999999999</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>lipophilicity_astrazeneca</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.472895</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.006499</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.0168949999999999</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>pgp_broccatelli</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9383629999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.003565</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.000363</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ppbr_az</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7.330617</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.098555</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1093830000000002</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>solubility_aqsoldb</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.738443</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.000456</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.002557</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>vdss_lombardo</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>full_v36_final</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.660995</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.004668</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.0520049999999999</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Final v36 validation-selected fixed endpoint configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ames</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.8359323660146076</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0117868323841928</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.0350676339853923</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.0360126339853922</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>bbb_martins</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8370934959349594</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0365172699261678</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.08690650406504059</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.0906855040650405</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>bioavailability_ma</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.4646491519787162</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0919538857623611</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.4773508480212837</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.2575988480212838</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>caco2_wang</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.178826145720296</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.5645614155222303</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.9228261457202958</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.8951791457202959</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>clearance_hepatocyte_az</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.1176104269364308</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1035212037797778</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.4183895730635691</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.434429573063569</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>clearance_microsome_az</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.4934948034061664</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0543683646759144</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.1365051965938336</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.1493191965938335</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cyp2c9_substrate_carbonmangels</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.3416119867851612</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.08870738536614529</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.1323880132148387</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.1017580132148388</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cyp2c9_veith</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.7747715915666096</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.013460594509409</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.0842284084333904</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.0158144084333905</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cyp2d6_substrate_carbonmangels</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.3054278126732336</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1174235518594523</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.4305721873267663</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.4421031873267662</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cyp2d6_veith</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.6300957083680512</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.07613565003254411</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.1599042916319488</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.0890762916319488</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cyp3a4_substrate_carbonmangels</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.4806509945750452</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.114788890799292</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.1863490054249548</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.2445980054249547</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cyp3a4_veith</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.8420451423300106</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0205152234881339</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.0739548576699894</v>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.0420758576699895</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dili</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.3225217391304348</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.3006986823092729</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.6334782608695652</v>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.5860872608695653</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>half_life_obach</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.0734604998065737</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1446836631753019</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-0.6494604998065737</v>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-0.5648504998065739</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>herg</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.5385272459499264</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.2043925191652601</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.3414727540500736</v>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.3248307540500736</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>hia_hou</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.9132510288065844</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0439197036824683</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-0.0797489711934157</v>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-0.08102897119341571</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ld50_zhu</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.6429992578096553</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0061257483383048</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0.0909992578096552</v>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-0.0399282578096553</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>lipophilicity_astrazeneca</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.529591568581974</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.0052434361806502</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-0.0735915685819739</v>
+      </c>
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-0.056696568581974</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>pgp_broccatelli</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.5837909890695815</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.3535486206060432</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-0.3542090109304184</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-0.3545720109304184</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ppbr_az</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.55136100354298</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.832259456883135</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-15.11136100354298</v>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-15.22074400354298</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>solubility_aqsoldb</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.8448780538544296</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0188436976027758</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-0.1038780538544296</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-0.1064350538544296</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>vdss_lombardo</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_v1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.1627848777552878</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0390776859796327</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-0.5502151222447121</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-0.4982101222447122</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ames</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.7893710470148232</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0187565532957392</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-0.08162895298517681</v>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.0825739529851767</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>bbb_martins</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.6746208567854909</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0318903505112522</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-0.2493791432145091</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-0.2531581432145091</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>bioavailability_ma</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.5364150315929498</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0448595110845819</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-0.4055849684070501</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-0.1858329684070502</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>caco2_wang</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.142599569908157</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.7178321720494956</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-0.8865995699081572</v>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-0.8589525699081574</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>clearance_hepatocyte_az</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.1950610669871612</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0846660207398926</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-0.3409389330128387</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-0.3569789330128386</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>clearance_microsome_az</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1368286804537397</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.0673741861596225</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-0.4931713195462602</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-0.5059853195462601</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cyp2c9_substrate_carbonmangels</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.3077341515097825</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.0412040835292789</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-0.1662658484902174</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-0.1356358484902175</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cyp2c9_veith</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.6994664784690434</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.0210369910975321</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-0.1595335215309565</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-0.09111952153095659</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cyp2d6_substrate_carbonmangels</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.5128442308004126</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.0461130660027658</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-0.2231557691995873</v>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-0.2346867691995872</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cyp2d6_veith</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.6283695043838655</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0131027840656666</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-0.1616304956161345</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-0.0908024956161345</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cyp3a4_substrate_carbonmangels</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.6134267631103074</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.0105265151885785</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-0.0535732368896926</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-0.1118222368896925</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cyp3a4_veith</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AUPRC</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.8362721868996058</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.0167959656288301</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-0.0797278131003942</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.0478488131003943</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>dili</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.0283168342190477</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-0.1509999999999999</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.103609</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>half_life_obach</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.1009519783186824</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.1366849372323874</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-0.4750480216813175</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-0.3904380216813176</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>herg</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.6142562592047128</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.07794928381059139</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-0.2657437407952872</v>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-0.2491017407952871</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>hia_hou</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.976625514403292</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.0028421887489435</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-0.0163744855967078</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-0.0176544855967078</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ld50_zhu</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.6419436718569442</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.0188882469685591</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-0.0899436718569441</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-0.0388726718569442</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>lipophilicity_astrazeneca</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.6064733263481816</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.0300942527479946</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-0.1504733263481816</v>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-0.1335783263481817</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>pgp_broccatelli</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AUROC</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.855385230605172</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.0138322870413809</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-0.0826147693948279</v>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-0.0829777693948279</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ppbr_az</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>11.52843807010037</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.5928436853428585</v>
+      </c>
+      <c r="H65" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-4.088438070100366</v>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-4.197821070100366</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>solubility_aqsoldb</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.8238269255755636</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.0109846796672376</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-0.0828269255755635</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-0.0853839255755636</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>vdss_lombardo</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>mlp_stacking_baseline_lbfgs_v1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.0889325156345888</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.1229932250056059</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-0.624067484365411</v>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-0.5720624843654112</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Fixed diagnostic LBFGS-MLP stacker trained on official-valid seed-mean candidate predictions; hyperparameters fixed a priori; official test used only for final reporting.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -47451,7 +50427,6 @@
       <c r="M2" t="b">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -47507,7 +50482,6 @@
       <c r="M3" t="b">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -47563,7 +50537,6 @@
       <c r="M4" t="b">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -47619,7 +50592,6 @@
       <c r="M5" t="b">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -47675,7 +50647,6 @@
       <c r="M6" t="b">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -47791,7 +50762,6 @@
       <c r="M8" t="b">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -47847,7 +50817,6 @@
       <c r="M9" t="b">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -47903,7 +50872,6 @@
       <c r="M10" t="b">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -47959,7 +50927,6 @@
       <c r="M11" t="b">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -48015,7 +50982,6 @@
       <c r="M12" t="b">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -48131,7 +51097,6 @@
       <c r="M14" t="b">
         <v>0</v>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -48187,7 +51152,6 @@
       <c r="M15" t="b">
         <v>0</v>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -48243,7 +51207,6 @@
       <c r="M16" t="b">
         <v>0</v>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -48299,7 +51262,6 @@
       <c r="M17" t="b">
         <v>0</v>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48355,7 +51317,6 @@
       <c r="M18" t="b">
         <v>0</v>
       </c>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48471,7 +51432,6 @@
       <c r="M20" t="b">
         <v>0</v>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -48527,7 +51487,6 @@
       <c r="M21" t="b">
         <v>0</v>
       </c>
-      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -48583,7 +51542,6 @@
       <c r="M22" t="b">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -48639,7 +51597,6 @@
       <c r="M23" t="b">
         <v>0</v>
       </c>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -48695,7 +51652,6 @@
       <c r="M24" t="b">
         <v>0</v>
       </c>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -48811,7 +51767,6 @@
       <c r="M26" t="b">
         <v>0</v>
       </c>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -48867,7 +51822,6 @@
       <c r="M27" t="b">
         <v>0</v>
       </c>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -48923,7 +51877,6 @@
       <c r="M28" t="b">
         <v>0</v>
       </c>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -48979,7 +51932,6 @@
       <c r="M29" t="b">
         <v>0</v>
       </c>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -49035,7 +51987,6 @@
       <c r="M30" t="b">
         <v>0</v>
       </c>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -49151,7 +52102,6 @@
       <c r="M32" t="b">
         <v>0</v>
       </c>
-      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -49207,7 +52157,6 @@
       <c r="M33" t="b">
         <v>0</v>
       </c>
-      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -49263,7 +52212,6 @@
       <c r="M34" t="b">
         <v>0</v>
       </c>
-      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -49319,7 +52267,6 @@
       <c r="M35" t="b">
         <v>0</v>
       </c>
-      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -49375,7 +52322,6 @@
       <c r="M36" t="b">
         <v>0</v>
       </c>
-      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -49491,7 +52437,6 @@
       <c r="M38" t="b">
         <v>0</v>
       </c>
-      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -49547,7 +52492,6 @@
       <c r="M39" t="b">
         <v>0</v>
       </c>
-      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -49603,7 +52547,6 @@
       <c r="M40" t="b">
         <v>0</v>
       </c>
-      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -49659,7 +52602,6 @@
       <c r="M41" t="b">
         <v>0</v>
       </c>
-      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -49715,7 +52657,6 @@
       <c r="M42" t="b">
         <v>0</v>
       </c>
-      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -49831,7 +52772,6 @@
       <c r="M44" t="b">
         <v>0</v>
       </c>
-      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -49887,7 +52827,6 @@
       <c r="M45" t="b">
         <v>0</v>
       </c>
-      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -49943,7 +52882,6 @@
       <c r="M46" t="b">
         <v>0</v>
       </c>
-      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -49999,7 +52937,6 @@
       <c r="M47" t="b">
         <v>0</v>
       </c>
-      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -50055,7 +52992,6 @@
       <c r="M48" t="b">
         <v>0</v>
       </c>
-      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -50171,7 +53107,6 @@
       <c r="M50" t="b">
         <v>0</v>
       </c>
-      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -50227,7 +53162,6 @@
       <c r="M51" t="b">
         <v>0</v>
       </c>
-      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -50283,7 +53217,6 @@
       <c r="M52" t="b">
         <v>0</v>
       </c>
-      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -50339,7 +53272,6 @@
       <c r="M53" t="b">
         <v>0</v>
       </c>
-      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -50395,7 +53327,6 @@
       <c r="M54" t="b">
         <v>0</v>
       </c>
-      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -50511,7 +53442,6 @@
       <c r="M56" t="b">
         <v>0</v>
       </c>
-      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -50567,7 +53497,6 @@
       <c r="M57" t="b">
         <v>0</v>
       </c>
-      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -50623,7 +53552,6 @@
       <c r="M58" t="b">
         <v>0</v>
       </c>
-      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -50679,7 +53607,6 @@
       <c r="M59" t="b">
         <v>0</v>
       </c>
-      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -50735,7 +53662,6 @@
       <c r="M60" t="b">
         <v>0</v>
       </c>
-      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -50851,7 +53777,6 @@
       <c r="M62" t="b">
         <v>0</v>
       </c>
-      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -50907,7 +53832,6 @@
       <c r="M63" t="b">
         <v>0</v>
       </c>
-      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -50963,7 +53887,6 @@
       <c r="M64" t="b">
         <v>0</v>
       </c>
-      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -51019,7 +53942,6 @@
       <c r="M65" t="b">
         <v>0</v>
       </c>
-      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -51075,7 +53997,6 @@
       <c r="M66" t="b">
         <v>0</v>
       </c>
-      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -51191,7 +54112,6 @@
       <c r="M68" t="b">
         <v>0</v>
       </c>
-      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -51247,7 +54167,6 @@
       <c r="M69" t="b">
         <v>0</v>
       </c>
-      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -51303,7 +54222,6 @@
       <c r="M70" t="b">
         <v>0</v>
       </c>
-      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -51359,7 +54277,6 @@
       <c r="M71" t="b">
         <v>0</v>
       </c>
-      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -51415,7 +54332,6 @@
       <c r="M72" t="b">
         <v>0</v>
       </c>
-      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -51531,7 +54447,6 @@
       <c r="M74" t="b">
         <v>0</v>
       </c>
-      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -51587,7 +54502,6 @@
       <c r="M75" t="b">
         <v>0</v>
       </c>
-      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -51643,7 +54557,6 @@
       <c r="M76" t="b">
         <v>0</v>
       </c>
-      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -51699,7 +54612,6 @@
       <c r="M77" t="b">
         <v>0</v>
       </c>
-      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -51755,7 +54667,6 @@
       <c r="M78" t="b">
         <v>0</v>
       </c>
-      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -51871,7 +54782,6 @@
       <c r="M80" t="b">
         <v>0</v>
       </c>
-      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -51927,7 +54837,6 @@
       <c r="M81" t="b">
         <v>0</v>
       </c>
-      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -51983,7 +54892,6 @@
       <c r="M82" t="b">
         <v>0</v>
       </c>
-      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -52039,7 +54947,6 @@
       <c r="M83" t="b">
         <v>0</v>
       </c>
-      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -52095,7 +55002,6 @@
       <c r="M84" t="b">
         <v>0</v>
       </c>
-      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -52211,7 +55117,6 @@
       <c r="M86" t="b">
         <v>0</v>
       </c>
-      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -52267,7 +55172,6 @@
       <c r="M87" t="b">
         <v>0</v>
       </c>
-      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -52323,7 +55227,6 @@
       <c r="M88" t="b">
         <v>0</v>
       </c>
-      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -52379,7 +55282,6 @@
       <c r="M89" t="b">
         <v>0</v>
       </c>
-      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -52435,7 +55337,6 @@
       <c r="M90" t="b">
         <v>0</v>
       </c>
-      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -52551,7 +55452,6 @@
       <c r="M92" t="b">
         <v>0</v>
       </c>
-      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -52607,7 +55507,6 @@
       <c r="M93" t="b">
         <v>0</v>
       </c>
-      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -52663,7 +55562,6 @@
       <c r="M94" t="b">
         <v>0</v>
       </c>
-      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -52719,7 +55617,6 @@
       <c r="M95" t="b">
         <v>0</v>
       </c>
-      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -52775,7 +55672,6 @@
       <c r="M96" t="b">
         <v>0</v>
       </c>
-      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -52891,7 +55787,6 @@
       <c r="M98" t="b">
         <v>0</v>
       </c>
-      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -52947,7 +55842,6 @@
       <c r="M99" t="b">
         <v>0</v>
       </c>
-      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -53003,7 +55897,6 @@
       <c r="M100" t="b">
         <v>0</v>
       </c>
-      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -53059,7 +55952,6 @@
       <c r="M101" t="b">
         <v>0</v>
       </c>
-      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -53115,7 +56007,6 @@
       <c r="M102" t="b">
         <v>0</v>
       </c>
-      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -53231,7 +56122,6 @@
       <c r="M104" t="b">
         <v>0</v>
       </c>
-      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -53287,7 +56177,6 @@
       <c r="M105" t="b">
         <v>0</v>
       </c>
-      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -53343,7 +56232,6 @@
       <c r="M106" t="b">
         <v>0</v>
       </c>
-      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -53399,7 +56287,6 @@
       <c r="M107" t="b">
         <v>0</v>
       </c>
-      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -53455,7 +56342,6 @@
       <c r="M108" t="b">
         <v>0</v>
       </c>
-      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -53571,7 +56457,6 @@
       <c r="M110" t="b">
         <v>0</v>
       </c>
-      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -53627,7 +56512,6 @@
       <c r="M111" t="b">
         <v>0</v>
       </c>
-      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -53683,7 +56567,6 @@
       <c r="M112" t="b">
         <v>0</v>
       </c>
-      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -53739,7 +56622,6 @@
       <c r="M113" t="b">
         <v>0</v>
       </c>
-      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -53795,7 +56677,6 @@
       <c r="M114" t="b">
         <v>0</v>
       </c>
-      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -53911,7 +56792,6 @@
       <c r="M116" t="b">
         <v>0</v>
       </c>
-      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -53967,7 +56847,6 @@
       <c r="M117" t="b">
         <v>0</v>
       </c>
-      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -54023,7 +56902,6 @@
       <c r="M118" t="b">
         <v>0</v>
       </c>
-      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -54079,7 +56957,6 @@
       <c r="M119" t="b">
         <v>0</v>
       </c>
-      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -54135,7 +57012,6 @@
       <c r="M120" t="b">
         <v>0</v>
       </c>
-      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -54251,7 +57127,6 @@
       <c r="M122" t="b">
         <v>0</v>
       </c>
-      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -54307,7 +57182,6 @@
       <c r="M123" t="b">
         <v>0</v>
       </c>
-      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -54363,7 +57237,6 @@
       <c r="M124" t="b">
         <v>0</v>
       </c>
-      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -54419,7 +57292,6 @@
       <c r="M125" t="b">
         <v>0</v>
       </c>
-      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -54475,7 +57347,6 @@
       <c r="M126" t="b">
         <v>0</v>
       </c>
-      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -54591,7 +57462,6 @@
       <c r="M128" t="b">
         <v>0</v>
       </c>
-      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -54647,7 +57517,6 @@
       <c r="M129" t="b">
         <v>0</v>
       </c>
-      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -54703,7 +57572,6 @@
       <c r="M130" t="b">
         <v>0</v>
       </c>
-      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -54759,7 +57627,6 @@
       <c r="M131" t="b">
         <v>0</v>
       </c>
-      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -54815,7 +57682,6 @@
       <c r="M132" t="b">
         <v>0</v>
       </c>
-      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -55371,8 +58237,6 @@
           <t>repeated tabular ensemble; xgboost_500; 5 formal seeds with internal repeated scaffold fold-bag</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -55395,7 +58259,6 @@
       <c r="U2" t="b">
         <v>1</v>
       </c>
-      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -55449,8 +58312,6 @@
           <t>ExtraTrees over chemical descriptors/fingerprints</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -55473,7 +58334,6 @@
       <c r="U3" t="b">
         <v>0</v>
       </c>
-      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -55527,8 +58387,6 @@
           <t>Canonical backup uses chem fixed chemical endpoint: kpgt/chem_core_pair_torsion/extratrees/topk=all; formal seeds=101,202,303,404,505.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -55551,7 +58409,6 @@
       <c r="U4" t="b">
         <v>1</v>
       </c>
-      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -55605,8 +58462,6 @@
           <t>Canonical backup uses chem fixed chemical endpoint: chemberta_kpgt/chem_core_pair_torsion/extratrees/topk=512; formal seeds=101,202,303,404,505.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -55629,7 +58484,6 @@
       <c r="U5" t="b">
         <v>1</v>
       </c>
-      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -55683,8 +58537,6 @@
           <t>clearance family-transfer XGB; fingerprint-only; valid_adjusted selector</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -55707,7 +58559,6 @@
       <c r="U6" t="b">
         <v>0</v>
       </c>
-      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -55761,8 +58612,6 @@
           <t>KPGT+EPT seedbag_5x5; equal seed-bag average</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -55785,7 +58634,6 @@
       <c r="U7" t="b">
         <v>1</v>
       </c>
-      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -55839,8 +58687,6 @@
           <t>Canonical backup uses xl fixed chemical endpoint: xl_v4_kpgt/embed_chem_xl_full_chemical_prior/xgb/topk=1024; formal seeds=101,202,303,404,505.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -55863,7 +58709,6 @@
       <c r="U8" t="b">
         <v>1</v>
       </c>
-      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -55917,8 +58762,6 @@
           <t>Canonical backup uses chem fixed chemical endpoint: kpgt_ept/chem_wide_chem/xgb/topk=all; formal seeds=101,202,303,404,505.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -55941,7 +58784,6 @@
       <c r="U9" t="b">
         <v>1</v>
       </c>
-      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -55995,8 +58837,6 @@
           <t>zscore(0.8*AP_surrogate_seedbag + 0.1*XL + 0.1*descriptor_sidecar_v2)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -56019,7 +58859,6 @@
       <c r="U10" t="b">
         <v>1</v>
       </c>
-      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -56073,8 +58912,6 @@
           <t>rank(0.4*K+E CE seedbag + 0.3*K+E FP/base_pred sidecar + 0.2*K+E AP + 0.1*tabular FP)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -56097,7 +58934,6 @@
       <c r="U11" t="b">
         <v>1</v>
       </c>
-      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -56151,8 +58987,6 @@
           <t>CYP substrate family-transfer pooled XGB; fingerprint-only; task one-hot</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -56175,7 +59009,6 @@
       <c r="U12" t="b">
         <v>0</v>
       </c>
-      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -56229,8 +59062,6 @@
           <t>logit(0.2*XL_K+E + 0.3*K+E CE seedbag + 0.3*K+E AP + 0.2*tabular FP)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -56253,7 +59084,6 @@
       <c r="U13" t="b">
         <v>1</v>
       </c>
-      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -56307,8 +59137,6 @@
           <t>raw(0.6*XL_K+E + 0.2*K+E CE seedbag + 0.2*K+E descriptor sidecar)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -56331,7 +59159,6 @@
       <c r="U14" t="b">
         <v>1</v>
       </c>
-      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -56385,8 +59212,6 @@
           <t>zscore(0.5*C+K metric_auto + 0.1*C+K Spearman seedbag + 0.4*C+K descriptor sidecar)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -56409,7 +59234,6 @@
       <c r="U15" t="b">
         <v>1</v>
       </c>
-      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -56463,8 +59287,6 @@
           <t>Canonical backup uses xl fixed chemical endpoint: xl_v4_ept/embed_chem_xl_morgan_family/extratrees/topk=all; formal seeds=101,202,303,404,505.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -56487,7 +59309,6 @@
       <c r="U16" t="b">
         <v>1</v>
       </c>
-      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -56541,8 +59362,6 @@
           <t>rank(0.1*selected_gated_5seed + 0.5*official_sidecar_bagged + 0.4*chem_logreg_trainonly); valid-only saturated-valid tie-break; true seed-varying 5-run final scores</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -56565,7 +59384,6 @@
       <c r="U17" t="b">
         <v>1</v>
       </c>
-      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -56619,8 +59437,6 @@
           <t>Canonical backup uses xl fixed chemical endpoint: xl_v4_chemberta_kpgt/chem_xl_full_chemical_prior/xgb/topk=4096; formal seeds=101,202,303,404,505.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -56643,7 +59459,6 @@
       <c r="U18" t="b">
         <v>1</v>
       </c>
-      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -56697,8 +59512,6 @@
           <t>raw(0.2*XL_K + 0.1*tabular FP + 0.3*K metric_auto + 0.4*K SmoothL1 seedbag)</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -56721,7 +59534,6 @@
       <c r="U19" t="b">
         <v>1</v>
       </c>
-      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -56775,8 +59587,6 @@
           <t>logit(0.65*layerwise_selected_gated + 0.25*aux_K+E + 0.10*aux_K)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -56799,7 +59609,6 @@
       <c r="U20" t="b">
         <v>0</v>
       </c>
-      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -56853,8 +59662,6 @@
           <t>0.7*KPGT_seedbag + 0.3*fp_only</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -56877,7 +59684,6 @@
       <c r="U21" t="b">
         <v>1</v>
       </c>
-      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -56931,8 +59737,6 @@
           <t>0.3*FP-XGB + 0.3*metric_auto(K+E) + 0.4*XL_v4</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -56955,7 +59759,6 @@
       <c r="U22" t="b">
         <v>0</v>
       </c>
-      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -57009,8 +59812,6 @@
           <t>rank(0.9*KPGT+EPT Spearman seedbag + 0.1*KPGT+EPT descriptor sidecar)</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>results_strict/final_22task_score_config_table_v36.csv</t>
@@ -57033,7 +59834,6 @@
       <c r="U23" t="b">
         <v>1</v>
       </c>
-      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -57117,7 +59917,6 @@
       <c r="U24" t="b">
         <v>0</v>
       </c>
-      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -57201,7 +60000,6 @@
       <c r="U25" t="b">
         <v>0</v>
       </c>
-      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -57285,7 +60083,6 @@
       <c r="U26" t="b">
         <v>0</v>
       </c>
-      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -57369,7 +60166,6 @@
       <c r="U27" t="b">
         <v>0</v>
       </c>
-      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -57453,7 +60249,6 @@
       <c r="U28" t="b">
         <v>0</v>
       </c>
-      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -57537,7 +60332,6 @@
       <c r="U29" t="b">
         <v>0</v>
       </c>
-      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -57621,7 +60415,6 @@
       <c r="U30" t="b">
         <v>0</v>
       </c>
-      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -57705,7 +60498,6 @@
       <c r="U31" t="b">
         <v>0</v>
       </c>
-      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -57789,7 +60581,6 @@
       <c r="U32" t="b">
         <v>0</v>
       </c>
-      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -57873,7 +60664,6 @@
       <c r="U33" t="b">
         <v>0</v>
       </c>
-      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -57957,7 +60747,6 @@
       <c r="U34" t="b">
         <v>0</v>
       </c>
-      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -58041,7 +60830,6 @@
       <c r="U35" t="b">
         <v>0</v>
       </c>
-      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -58125,7 +60913,6 @@
       <c r="U36" t="b">
         <v>0</v>
       </c>
-      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -58209,7 +60996,6 @@
       <c r="U37" t="b">
         <v>0</v>
       </c>
-      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -58293,7 +61079,6 @@
       <c r="U38" t="b">
         <v>0</v>
       </c>
-      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -58377,7 +61162,6 @@
       <c r="U39" t="b">
         <v>0</v>
       </c>
-      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -58461,7 +61245,6 @@
       <c r="U40" t="b">
         <v>0</v>
       </c>
-      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -58545,7 +61328,6 @@
       <c r="U41" t="b">
         <v>0</v>
       </c>
-      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -58629,7 +61411,6 @@
       <c r="U42" t="b">
         <v>0</v>
       </c>
-      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -58713,7 +61494,6 @@
       <c r="U43" t="b">
         <v>0</v>
       </c>
-      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -58797,7 +61577,6 @@
       <c r="U44" t="b">
         <v>0</v>
       </c>
-      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -58881,7 +61660,6 @@
       <c r="U45" t="b">
         <v>0</v>
       </c>
-      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -58965,7 +61743,6 @@
       <c r="U46" t="b">
         <v>0</v>
       </c>
-      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -59049,7 +61826,6 @@
       <c r="U47" t="b">
         <v>0</v>
       </c>
-      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -59133,7 +61909,6 @@
       <c r="U48" t="b">
         <v>0</v>
       </c>
-      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -59217,7 +61992,6 @@
       <c r="U49" t="b">
         <v>0</v>
       </c>
-      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -59301,7 +62075,6 @@
       <c r="U50" t="b">
         <v>0</v>
       </c>
-      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -59385,7 +62158,6 @@
       <c r="U51" t="b">
         <v>0</v>
       </c>
-      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -59469,7 +62241,6 @@
       <c r="U52" t="b">
         <v>0</v>
       </c>
-      <c r="V52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -59553,7 +62324,6 @@
       <c r="U53" t="b">
         <v>0</v>
       </c>
-      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -59637,7 +62407,6 @@
       <c r="U54" t="b">
         <v>0</v>
       </c>
-      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -59721,7 +62490,6 @@
       <c r="U55" t="b">
         <v>0</v>
       </c>
-      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -59805,7 +62573,6 @@
       <c r="U56" t="b">
         <v>0</v>
       </c>
-      <c r="V56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -59889,7 +62656,6 @@
       <c r="U57" t="b">
         <v>0</v>
       </c>
-      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -59973,7 +62739,6 @@
       <c r="U58" t="b">
         <v>0</v>
       </c>
-      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -60057,7 +62822,6 @@
       <c r="U59" t="b">
         <v>0</v>
       </c>
-      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -60141,7 +62905,6 @@
       <c r="U60" t="b">
         <v>0</v>
       </c>
-      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -60225,7 +62988,6 @@
       <c r="U61" t="b">
         <v>0</v>
       </c>
-      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -60309,7 +63071,6 @@
       <c r="U62" t="b">
         <v>0</v>
       </c>
-      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -60393,7 +63154,6 @@
       <c r="U63" t="b">
         <v>0</v>
       </c>
-      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -60477,7 +63237,6 @@
       <c r="U64" t="b">
         <v>0</v>
       </c>
-      <c r="V64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -60561,7 +63320,6 @@
       <c r="U65" t="b">
         <v>0</v>
       </c>
-      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -60645,7 +63403,6 @@
       <c r="U66" t="b">
         <v>0</v>
       </c>
-      <c r="V66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -60729,7 +63486,6 @@
       <c r="U67" t="b">
         <v>0</v>
       </c>
-      <c r="V67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -60813,7 +63569,6 @@
       <c r="U68" t="b">
         <v>0</v>
       </c>
-      <c r="V68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -60897,7 +63652,6 @@
       <c r="U69" t="b">
         <v>0</v>
       </c>
-      <c r="V69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -60981,7 +63735,6 @@
       <c r="U70" t="b">
         <v>0</v>
       </c>
-      <c r="V70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -61065,7 +63818,6 @@
       <c r="U71" t="b">
         <v>0</v>
       </c>
-      <c r="V71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -61149,7 +63901,6 @@
       <c r="U72" t="b">
         <v>0</v>
       </c>
-      <c r="V72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -61233,7 +63984,6 @@
       <c r="U73" t="b">
         <v>0</v>
       </c>
-      <c r="V73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -61317,7 +64067,6 @@
       <c r="U74" t="b">
         <v>0</v>
       </c>
-      <c r="V74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -61401,7 +64150,6 @@
       <c r="U75" t="b">
         <v>0</v>
       </c>
-      <c r="V75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -61485,7 +64233,6 @@
       <c r="U76" t="b">
         <v>0</v>
       </c>
-      <c r="V76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -61569,7 +64316,6 @@
       <c r="U77" t="b">
         <v>0</v>
       </c>
-      <c r="V77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -61653,7 +64399,6 @@
       <c r="U78" t="b">
         <v>0</v>
       </c>
-      <c r="V78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -61737,7 +64482,6 @@
       <c r="U79" t="b">
         <v>0</v>
       </c>
-      <c r="V79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -61821,7 +64565,6 @@
       <c r="U80" t="b">
         <v>0</v>
       </c>
-      <c r="V80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -61905,7 +64648,6 @@
       <c r="U81" t="b">
         <v>0</v>
       </c>
-      <c r="V81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -61989,7 +64731,6 @@
       <c r="U82" t="b">
         <v>0</v>
       </c>
-      <c r="V82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -62073,7 +64814,6 @@
       <c r="U83" t="b">
         <v>0</v>
       </c>
-      <c r="V83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -62157,7 +64897,6 @@
       <c r="U84" t="b">
         <v>0</v>
       </c>
-      <c r="V84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -62241,7 +64980,6 @@
       <c r="U85" t="b">
         <v>0</v>
       </c>
-      <c r="V85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -62325,7 +65063,6 @@
       <c r="U86" t="b">
         <v>0</v>
       </c>
-      <c r="V86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -62409,7 +65146,6 @@
       <c r="U87" t="b">
         <v>0</v>
       </c>
-      <c r="V87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -62493,7 +65229,6 @@
       <c r="U88" t="b">
         <v>0</v>
       </c>
-      <c r="V88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -62577,7 +65312,6 @@
       <c r="U89" t="b">
         <v>0</v>
       </c>
-      <c r="V89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -62606,7 +65340,6 @@
       <c r="F90" t="n">
         <v>0.8551077953357222</v>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>0.871</v>
       </c>
@@ -62659,7 +65392,6 @@
       <c r="U90" t="b">
         <v>0</v>
       </c>
-      <c r="V90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -62688,7 +65420,6 @@
       <c r="F91" t="n">
         <v>0.902439024390244</v>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>0.924</v>
       </c>
@@ -62741,7 +65472,6 @@
       <c r="U91" t="b">
         <v>0</v>
       </c>
-      <c r="V91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -62770,7 +65500,6 @@
       <c r="F92" t="n">
         <v>0.6458264050548721</v>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>0.9419999999999999</v>
       </c>
@@ -62823,7 +65552,6 @@
       <c r="U92" t="b">
         <v>0</v>
       </c>
-      <c r="V92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -62852,7 +65580,6 @@
       <c r="F93" t="n">
         <v>0.3520695007222605</v>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>0.256</v>
       </c>
@@ -62905,7 +65632,6 @@
       <c r="U93" t="b">
         <v>0</v>
       </c>
-      <c r="V93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -62934,7 +65660,6 @@
       <c r="F94" t="n">
         <v>0.1788322549824511</v>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>0.536</v>
       </c>
@@ -62987,7 +65712,6 @@
       <c r="U94" t="b">
         <v>0</v>
       </c>
-      <c r="V94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -63016,7 +65740,6 @@
       <c r="F95" t="n">
         <v>0.4382058069675574</v>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>0.63</v>
       </c>
@@ -63069,7 +65792,6 @@
       <c r="U95" t="b">
         <v>0</v>
       </c>
-      <c r="V95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -63098,7 +65820,6 @@
       <c r="F96" t="n">
         <v>0.4517016156517738</v>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>0.474</v>
       </c>
@@ -63151,7 +65872,6 @@
       <c r="U96" t="b">
         <v>0</v>
       </c>
-      <c r="V96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -63180,7 +65900,6 @@
       <c r="F97" t="n">
         <v>0.7700697697202045</v>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>0.859</v>
       </c>
@@ -63233,7 +65952,6 @@
       <c r="U97" t="b">
         <v>0</v>
       </c>
-      <c r="V97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -63262,7 +65980,6 @@
       <c r="F98" t="n">
         <v>0.6985240233492779</v>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>0.736</v>
       </c>
@@ -63315,7 +66032,6 @@
       <c r="U98" t="b">
         <v>0</v>
       </c>
-      <c r="V98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -63344,7 +66060,6 @@
       <c r="F99" t="n">
         <v>0.7008360219135269</v>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>0.79</v>
       </c>
@@ -63397,7 +66112,6 @@
       <c r="U99" t="b">
         <v>0</v>
       </c>
-      <c r="V99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -63426,7 +66140,6 @@
       <c r="F100" t="n">
         <v>0.6734855334538878</v>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>0.667</v>
       </c>
@@ -63479,7 +66192,6 @@
       <c r="U100" t="b">
         <v>0</v>
       </c>
-      <c r="V100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -63508,7 +66220,6 @@
       <c r="F101" t="n">
         <v>0.8623033394316458</v>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>0.916</v>
       </c>
@@ -63561,7 +66272,6 @@
       <c r="U101" t="b">
         <v>0</v>
       </c>
-      <c r="V101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -63590,7 +66300,6 @@
       <c r="F102" t="n">
         <v>0.8578260869565217</v>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>0.956</v>
       </c>
@@ -63643,7 +66352,6 @@
       <c r="U102" t="b">
         <v>0</v>
       </c>
-      <c r="V102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -63672,7 +66380,6 @@
       <c r="F103" t="n">
         <v>0.4196225087944947</v>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>0.576</v>
       </c>
@@ -63725,7 +66432,6 @@
       <c r="U103" t="b">
         <v>0</v>
       </c>
-      <c r="V103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -63754,7 +66460,6 @@
       <c r="F104" t="n">
         <v>0.804860088365243</v>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>0.88</v>
       </c>
@@ -63807,7 +66512,6 @@
       <c r="U104" t="b">
         <v>0</v>
       </c>
-      <c r="V104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -63836,7 +66540,6 @@
       <c r="F105" t="n">
         <v>0.9456790123456792</v>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>0.993</v>
       </c>
@@ -63889,7 +66592,6 @@
       <c r="U105" t="b">
         <v>0</v>
       </c>
-      <c r="V105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -63918,7 +66620,6 @@
       <c r="F106" t="n">
         <v>0.6218126123432216</v>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>0.552</v>
       </c>
@@ -63971,7 +66672,6 @@
       <c r="U106" t="b">
         <v>0</v>
       </c>
-      <c r="V106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -64000,7 +66700,6 @@
       <c r="F107" t="n">
         <v>0.5572363431113107</v>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>0.456</v>
       </c>
@@ -64053,7 +66752,6 @@
       <c r="U107" t="b">
         <v>0</v>
       </c>
-      <c r="V107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -64082,7 +66780,6 @@
       <c r="F108" t="n">
         <v>0.9273527059450812</v>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>0.9379999999999999</v>
       </c>
@@ -64135,7 +66832,6 @@
       <c r="U108" t="b">
         <v>0</v>
       </c>
-      <c r="V108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -64164,7 +66860,6 @@
       <c r="F109" t="n">
         <v>9.118758898412606</v>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>7.44</v>
       </c>
@@ -64217,7 +66912,6 @@
       <c r="U109" t="b">
         <v>0</v>
       </c>
-      <c r="V109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -64246,7 +66940,6 @@
       <c r="F110" t="n">
         <v>0.8359848801021843</v>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>0.741</v>
       </c>
@@ -64299,7 +66992,6 @@
       <c r="U110" t="b">
         <v>0</v>
       </c>
-      <c r="V110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -64328,7 +67020,6 @@
       <c r="F111" t="n">
         <v>0.4798305110695061</v>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>0.713</v>
       </c>
@@ -64381,7 +67072,6 @@
       <c r="U111" t="b">
         <v>0</v>
       </c>
-      <c r="V111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -64465,7 +67155,6 @@
       <c r="U112" t="b">
         <v>0</v>
       </c>
-      <c r="V112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -64549,7 +67238,6 @@
       <c r="U113" t="b">
         <v>0</v>
       </c>
-      <c r="V113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -64633,7 +67321,6 @@
       <c r="U114" t="b">
         <v>0</v>
       </c>
-      <c r="V114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -64717,7 +67404,6 @@
       <c r="U115" t="b">
         <v>0</v>
       </c>
-      <c r="V115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -64801,7 +67487,6 @@
       <c r="U116" t="b">
         <v>0</v>
       </c>
-      <c r="V116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -64885,7 +67570,6 @@
       <c r="U117" t="b">
         <v>0</v>
       </c>
-      <c r="V117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -64969,7 +67653,6 @@
       <c r="U118" t="b">
         <v>0</v>
       </c>
-      <c r="V118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -65053,7 +67736,6 @@
       <c r="U119" t="b">
         <v>0</v>
       </c>
-      <c r="V119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -65137,7 +67819,6 @@
       <c r="U120" t="b">
         <v>0</v>
       </c>
-      <c r="V120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -65221,7 +67902,6 @@
       <c r="U121" t="b">
         <v>0</v>
       </c>
-      <c r="V121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -65305,7 +67985,6 @@
       <c r="U122" t="b">
         <v>0</v>
       </c>
-      <c r="V122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -65389,7 +68068,6 @@
       <c r="U123" t="b">
         <v>0</v>
       </c>
-      <c r="V123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -65473,7 +68151,6 @@
       <c r="U124" t="b">
         <v>0</v>
       </c>
-      <c r="V124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -65557,7 +68234,6 @@
       <c r="U125" t="b">
         <v>0</v>
       </c>
-      <c r="V125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -65641,7 +68317,6 @@
       <c r="U126" t="b">
         <v>0</v>
       </c>
-      <c r="V126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -65725,7 +68400,6 @@
       <c r="U127" t="b">
         <v>0</v>
       </c>
-      <c r="V127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -65809,7 +68483,6 @@
       <c r="U128" t="b">
         <v>0</v>
       </c>
-      <c r="V128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -65893,7 +68566,6 @@
       <c r="U129" t="b">
         <v>0</v>
       </c>
-      <c r="V129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -65977,7 +68649,6 @@
       <c r="U130" t="b">
         <v>0</v>
       </c>
-      <c r="V130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -66061,7 +68732,6 @@
       <c r="U131" t="b">
         <v>0</v>
       </c>
-      <c r="V131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -66145,7 +68815,6 @@
       <c r="U132" t="b">
         <v>0</v>
       </c>
-      <c r="V132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -66229,7 +68898,6 @@
       <c r="U133" t="b">
         <v>0</v>
       </c>
-      <c r="V133" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/supplementary_tables/Supplementary_Tables_S1_S18.xlsx
+++ b/supplementary_tables/Supplementary_Tables_S1_S18.xlsx
@@ -9174,7 +9174,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/ppbr_az/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/ppbr_az/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/ppbr_az/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/ppbr_az/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/clearance_hepatocyte_az/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/clearance_hepatocyte_az/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/clearance_microsome_az/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/clearance_microsome_az/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/vdss_lombardo/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/vdss_lombardo/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/pgp_broccatelli/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/pgp_broccatelli/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/hia_hou/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/hia_hou/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/cyp3a4_substrate_carbonmangels/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/cyp3a4_substrate_carbonmangels/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/caco2_wang/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/caco2_wang/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://github.com/dchen0212/trimole_hybird/results_strict/case_study_v36_exact_full/full_predictions/clearance_microsome_az/test_predictions_full_seed_mean.csv</t>
+          <t>https://github.com/dchen0212/trimole_hybrid/results_strict/case_study_v36_exact_full/full_predictions/clearance_microsome_az/test_predictions_full_seed_mean.csv</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -41915,7 +41915,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://github.com/dchen0212/trimole_hybird</t>
+          <t>https://github.com/dchen0212/trimole_hybrid</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -41977,7 +41977,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://github.com/dchen0212/trimole_hybird</t>
+          <t>https://github.com/dchen0212/trimole_hybrid</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
